--- a/data/trans_orig/P6711-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>23954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48939</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20887</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>30555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23334</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47805</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45248</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26553</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37611</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93163</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120798</t>
+          <t>121330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68580</t>
+          <t>68727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>92568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170716</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207640</t>
+          <t>206567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93346</t>
+          <t>94384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135652</t>
+          <t>136720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59593</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92691</t>
+          <t>93241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>162329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214012</t>
+          <t>213691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42953</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72551</t>
+          <t>73116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36394</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65355</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88278</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127845</t>
+          <t>126798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146591</t>
+          <t>147173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196710</t>
+          <t>195513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>75154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>111444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>231933</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296170</t>
+          <t>292089</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153561</t>
+          <t>155727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202808</t>
+          <t>204935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105076</t>
+          <t>103331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143096</t>
+          <t>143073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271962</t>
+          <t>271577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332873</t>
+          <t>332736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364592</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>425806</t>
+          <t>427616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211966</t>
+          <t>211294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258930</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>591060</t>
+          <t>596872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>669289</t>
+          <t>674306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28851</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>53570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83391</t>
+          <t>83735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>39037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54368</t>
+          <t>53914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92879</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23193</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>46718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90227</t>
+          <t>89864</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131479</t>
+          <t>130955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>72450</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108198</t>
+          <t>108395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118660</t>
+          <t>120814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156558</t>
+          <t>156760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90697</t>
+          <t>90988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123502</t>
+          <t>122965</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>221547</t>
+          <t>218501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>271998</t>
+          <t>270147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>133755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182789</t>
+          <t>182940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>110811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153210</t>
+          <t>155227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257802</t>
+          <t>257377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>323592</t>
+          <t>325118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>66939</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104156</t>
+          <t>106073</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57411</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>92112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133699</t>
+          <t>132965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185409</t>
+          <t>186373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>236813</t>
+          <t>233597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>296179</t>
+          <t>292938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116186</t>
+          <t>118912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164034</t>
+          <t>163235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>367431</t>
+          <t>368706</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>439905</t>
+          <t>440131</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231670</t>
+          <t>234692</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>292218</t>
+          <t>289188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156727</t>
+          <t>155172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206773</t>
+          <t>204670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>406087</t>
+          <t>403262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>479160</t>
+          <t>481737</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>604481</t>
+          <t>605803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>680676</t>
+          <t>682563</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>387895</t>
+          <t>391649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>454916</t>
+          <t>452514</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1014918</t>
+          <t>1014515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1113171</t>
+          <t>1116707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40944</t>
+          <t>41868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26757</t>
+          <t>27945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62324</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39931</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>57688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>53175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>71376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110817</t>
+          <t>110518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153975</t>
+          <t>155677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97959</t>
+          <t>99964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137269</t>
+          <t>140108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221872</t>
+          <t>222932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279470</t>
+          <t>282355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106280</t>
+          <t>105509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149028</t>
+          <t>150095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78252</t>
+          <t>79344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113729</t>
+          <t>114385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194358</t>
+          <t>196646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252179</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>193795</t>
+          <t>194895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246680</t>
+          <t>245720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134373</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177064</t>
+          <t>176133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>342248</t>
+          <t>343472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>409600</t>
+          <t>410293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187250</t>
+          <t>184679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238859</t>
+          <t>237450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116528</t>
+          <t>116590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161059</t>
+          <t>157289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311590</t>
+          <t>312932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379108</t>
+          <t>380476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207420</t>
+          <t>211207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263713</t>
+          <t>265453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125505</t>
+          <t>127754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>168734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353072</t>
+          <t>350925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424764</t>
+          <t>419284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>49658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>78888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97267</t>
+          <t>95578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138284</t>
+          <t>136369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47323</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>52332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92802</t>
+          <t>90959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>57920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>90178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46838</t>
+          <t>47263</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75589</t>
+          <t>75844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111539</t>
+          <t>112921</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156468</t>
+          <t>155685</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>65674</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98791</t>
+          <t>99853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41925</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>70516</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117428</t>
+          <t>116490</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160175</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91000</t>
+          <t>91129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127182</t>
+          <t>125272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>74474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107412</t>
+          <t>107633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>176323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224507</t>
+          <t>223469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>183302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238261</t>
+          <t>236136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>170241</t>
+          <t>168974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221300</t>
+          <t>220632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369840</t>
+          <t>365723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>443898</t>
+          <t>440482</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153811</t>
+          <t>157551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203762</t>
+          <t>208602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122907</t>
+          <t>120324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>165633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>293753</t>
+          <t>292652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>358656</t>
+          <t>362099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>291374</t>
+          <t>292088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>355407</t>
+          <t>355350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>209667</t>
+          <t>207887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>262897</t>
+          <t>260910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>516087</t>
+          <t>517785</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>595592</t>
+          <t>602041</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>289677</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>353997</t>
+          <t>350935</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>180480</t>
+          <t>182105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231084</t>
+          <t>232374</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>486144</t>
+          <t>486430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>572832</t>
+          <t>569075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351799</t>
+          <t>353232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>422617</t>
+          <t>420615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>227496</t>
+          <t>226655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>282976</t>
+          <t>286161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>600913</t>
+          <t>595032</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>686480</t>
+          <t>683608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6711-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>29073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>25646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30555</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47758</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46260</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67179</t>
+          <t>64262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94982</t>
+          <t>95073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121330</t>
+          <t>121224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68727</t>
+          <t>67606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92568</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>171197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206567</t>
+          <t>206868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,85%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94384</t>
+          <t>92021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136720</t>
+          <t>133354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93241</t>
+          <t>91214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162329</t>
+          <t>161215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213691</t>
+          <t>214888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73116</t>
+          <t>72304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85815</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126798</t>
+          <t>124461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147173</t>
+          <t>146216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195513</t>
+          <t>192892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75154</t>
+          <t>75195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111444</t>
+          <t>111262</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231933</t>
+          <t>235273</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>292089</t>
+          <t>296110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155727</t>
+          <t>155039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204935</t>
+          <t>204198</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103331</t>
+          <t>103557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143073</t>
+          <t>142054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271577</t>
+          <t>270209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332736</t>
+          <t>336088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367110</t>
+          <t>364383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427616</t>
+          <t>424637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211294</t>
+          <t>209257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259007</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596872</t>
+          <t>588067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>674306</t>
+          <t>666625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>28018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83735</t>
+          <t>83791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53914</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58542</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91842</t>
+          <t>92762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46718</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89864</t>
+          <t>90828</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130955</t>
+          <t>132459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>37935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>64585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53704</t>
+          <t>52968</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>71900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108395</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120814</t>
+          <t>120210</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156760</t>
+          <t>156946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90988</t>
+          <t>90569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122965</t>
+          <t>123129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>218501</t>
+          <t>217868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>270147</t>
+          <t>270718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133755</t>
+          <t>134547</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>182940</t>
+          <t>184148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110811</t>
+          <t>110405</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155227</t>
+          <t>153006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257377</t>
+          <t>260431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>325118</t>
+          <t>326392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68530</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106073</t>
+          <t>106445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92112</t>
+          <t>92936</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>132965</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186373</t>
+          <t>183138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>233597</t>
+          <t>234337</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292938</t>
+          <t>296799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>118912</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>163946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>368706</t>
+          <t>361797</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>440131</t>
+          <t>441849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>234692</t>
+          <t>235653</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>289188</t>
+          <t>294469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,47 +3131,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>178988</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>156724</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>206041</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>16,6%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>178988</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>155172</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>204670</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>403262</t>
+          <t>404504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>481737</t>
+          <t>484542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>605803</t>
+          <t>601500</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>682563</t>
+          <t>679772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>391649</t>
+          <t>390646</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>452514</t>
+          <t>454092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1014515</t>
+          <t>1014011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1116707</t>
+          <t>1116022</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>47748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>42086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>38311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>62927</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39712</t>
+          <t>39745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57688</t>
+          <t>55659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53175</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>24381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71376</t>
+          <t>71423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110518</t>
+          <t>109047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155677</t>
+          <t>153520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99964</t>
+          <t>99073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140108</t>
+          <t>140331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222932</t>
+          <t>222042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282355</t>
+          <t>278118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105509</t>
+          <t>103843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150095</t>
+          <t>147362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79344</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114385</t>
+          <t>114118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196646</t>
+          <t>196194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251277</t>
+          <t>253323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194895</t>
+          <t>193117</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245720</t>
+          <t>245320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133971</t>
+          <t>133365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176133</t>
+          <t>175155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>343472</t>
+          <t>343751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>410293</t>
+          <t>410023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184679</t>
+          <t>186892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237450</t>
+          <t>236274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116590</t>
+          <t>116995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157289</t>
+          <t>158270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>312932</t>
+          <t>309531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>380476</t>
+          <t>380513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211207</t>
+          <t>210524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265453</t>
+          <t>266331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127754</t>
+          <t>127247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168734</t>
+          <t>172269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350925</t>
+          <t>349761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419284</t>
+          <t>418368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49658</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78888</t>
+          <t>77536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95578</t>
+          <t>97838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136369</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>46062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>51159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60091</t>
+          <t>59195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90959</t>
+          <t>91110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>57586</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90178</t>
+          <t>88726</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75844</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>112333</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155685</t>
+          <t>153238</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65674</t>
+          <t>64476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99853</t>
+          <t>99235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44130</t>
+          <t>43551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70516</t>
+          <t>70151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116490</t>
+          <t>116601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160213</t>
+          <t>160825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91129</t>
+          <t>92592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125272</t>
+          <t>126007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>75088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107633</t>
+          <t>104951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176323</t>
+          <t>175168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223469</t>
+          <t>221433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183302</t>
+          <t>185087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236136</t>
+          <t>236752</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168974</t>
+          <t>169244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220632</t>
+          <t>219642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>365723</t>
+          <t>369360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>440482</t>
+          <t>442672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157551</t>
+          <t>155150</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208602</t>
+          <t>205739</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,82 +5864,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>143422</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>124772</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>167670</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>324306</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>290846</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>360522</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>14,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>143422</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>120324</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>165633</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>324306</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>292652</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>362099</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>292088</t>
+          <t>291226</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>355350</t>
+          <t>356421</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207887</t>
+          <t>209816</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>260910</t>
+          <t>262296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>517785</t>
+          <t>518035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>602041</t>
+          <t>605381</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>288323</t>
+          <t>290191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>350935</t>
+          <t>352599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>182105</t>
+          <t>179619</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232374</t>
+          <t>232484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>486430</t>
+          <t>483826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>569075</t>
+          <t>568577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>353232</t>
+          <t>354941</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>420615</t>
+          <t>425099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>226655</t>
+          <t>228356</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>286161</t>
+          <t>283130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>595032</t>
+          <t>593857</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>683608</t>
+          <t>688935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
